--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
@@ -885,7 +885,7 @@
       <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2001</t>
         </is>
       </c>
       <c r="G3" s="44" t="n"/>
@@ -1870,8 +1870,8 @@
     <mergeCell ref="A78:I78"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A25:I29"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A76:C76"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
@@ -885,7 +885,7 @@
       <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2001</t>
+15/15/2015</t>
         </is>
       </c>
       <c r="G3" s="44" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
@@ -885,7 +885,7 @@
       <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-15/15/2015</t>
+22/02/2025</t>
         </is>
       </c>
       <c r="G3" s="44" t="n"/>
@@ -1870,8 +1870,8 @@
     <mergeCell ref="A78:I78"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A25:I29"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A76:C76"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
@@ -885,7 +885,7 @@
       <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2000</t>
         </is>
       </c>
       <c r="G3" s="44" t="n"/>
@@ -1870,8 +1870,8 @@
     <mergeCell ref="A78:I78"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A25:I29"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A76:C76"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área de Ciencias Básicas/Matemáticas/16-Cálculo multivariado.xlsx
@@ -885,7 +885,7 @@
       <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2000</t>
+10/10/2000</t>
         </is>
       </c>
       <c r="G3" s="44" t="n"/>
